--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="48">
   <si>
     <t>code</t>
   </si>
@@ -32,6 +32,42 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>public-database</t>
+  </si>
+  <si>
+    <t>budget_alignment_guidance</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>10</t>
@@ -453,10 +489,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:MC11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:341">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -475,145 +511,1150 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ID1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="II1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LT1" t="s">
+        <v>8</v>
+      </c>
+      <c r="LU1" t="s">
+        <v>9</v>
+      </c>
+      <c r="LV1" t="s">
+        <v>10</v>
+      </c>
+      <c r="LW1" t="s">
+        <v>11</v>
+      </c>
+      <c r="LX1" t="s">
+        <v>12</v>
+      </c>
+      <c r="LY1" t="s">
+        <v>13</v>
+      </c>
+      <c r="LZ1" t="s">
+        <v>14</v>
+      </c>
+      <c r="MA1" t="s">
+        <v>15</v>
+      </c>
+      <c r="MB1" t="s">
+        <v>16</v>
+      </c>
+      <c r="MC1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:341">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:341">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:341">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:341">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:341">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:341">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:341">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:341">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:341">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:341">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>iso-alpha-3-code</t>
   </si>
   <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>sub-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
     <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>10</t>

--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
   </si>
   <si>
     <t>10</t>

--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>10</t>

--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>10</t>

--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
     <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
   </si>
   <si>
     <t>10</t>

--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>10</t>

--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -43,31 +43,31 @@
     <t>iso-alpha-3-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-code</t>
   </si>
   <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>10</t>

--- a/api/clv3/xlsx/en/FlowType.xlsx
+++ b/api/clv3/xlsx/en/FlowType.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>code</t>
   </si>
@@ -23,12 +23,6 @@
   </si>
   <si>
     <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>url</t>
   </si>
   <si>
     <t>status</t>
@@ -453,10 +447,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,151 +463,145 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
         <v>32</v>
       </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
